--- a/Lab-1/Requirements_Table.xlsx
+++ b/Lab-1/Requirements_Table.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86C628D9-7557-4967-A5D9-3F01FFE50B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC6A0CD7-FF75-40FA-9B38-6E2F69785ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>Drivers need to find a charger that their vehicle can actually use.</t>
+  </si>
+  <si>
+    <t>NAME:V.Saatwik      SRN:PES1UG24CS509.                   SECTION: I</t>
   </si>
   <si>
     <t>FR-002</t>
@@ -82,7 +85,7 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t>PASS: A successful reservation is created for the selected socket and time.                     FAIL</t>
+      <t>PASS: A successful reservation is created for the selected socket and time.                                                      FAIL</t>
     </r>
     <r>
       <rPr>
@@ -101,7 +104,7 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> The system creates a reservation without an available slot.</t>
+      <t xml:space="preserve"> The system creates a reservation without an available slot.         </t>
     </r>
   </si>
   <si>
@@ -117,7 +120,7 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>PASS: Reservation changes to cancelled status and the slot becomes available.         FAIL: Cancelled slot remains permanently unavailable.</t>
+    <t xml:space="preserve">PASS: Reservation changes to cancelled status and the slot becomes available.                         FAIL: Cancelled slot remains permanently unavailable. </t>
   </si>
   <si>
     <t>Driver may have to change their plans in case of personal reasons.</t>
@@ -129,7 +132,7 @@
     <t>The system shall prevent two drivers from reserving the same charging socket during overlapping time slots.</t>
   </si>
   <si>
-    <t>PASS: The second reservation causing the confict is rejected.                     FAIL: Two reservations exist for the same socket at the same time.</t>
+    <t>PASS: The second reservation causing the conflict is rejected.                     FAIL: Two reservations exist for the same socket at the same time.</t>
   </si>
   <si>
     <t>Preventing conflicts and personalizing reservations is necessary.</t>
@@ -156,7 +159,7 @@
     <t>The system shall maintain reservation information without losing confirmed bookings during normal system operation.</t>
   </si>
   <si>
-    <t>PASS: Confirmed reservations remain available after restarting the system.                  FAIL: A confirmed reservation disappears or becomes inconsistent.</t>
+    <t>PASS: Confirmed reservations remain available after restarting the system.                                         FAIL: A confirmed reservation disappears or becomes inconsistent.</t>
   </si>
   <si>
     <t>Losing a reservation may lead to duplicate bookings and inconvenience to the drivers.</t>
@@ -205,7 +208,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +227,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -247,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -255,11 +265,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -615,18 +634,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.28515625" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" customWidth="1"/>
     <col min="4" max="4" width="19.42578125" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="6" max="6" width="32.5703125" customWidth="1"/>
+    <col min="9" max="9" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6">
+    <row r="1" spans="1:9">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,8 +674,9 @@
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="96" customHeight="1">
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" spans="1:9" ht="96" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -665,176 +695,190 @@
       <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="123.75" customHeight="1">
+      <c r="G3" s="7"/>
+      <c r="I3" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="123.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>14</v>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="106.5" customHeight="1">
+        <v>16</v>
+      </c>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:9" ht="106.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="E5" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="111.75" customHeight="1">
+        <v>21</v>
+      </c>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" ht="111.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="192" customHeight="1">
+        <v>25</v>
+      </c>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:9" ht="192" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="134.25" customHeight="1">
+        <v>29</v>
+      </c>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" ht="134.25" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>32</v>
+      <c r="E8" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="148.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:9" ht="148.5" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>38</v>
+      </c>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
